--- a/main/ig/StructureDefinition-lm-identity.xlsx
+++ b/main/ig/StructureDefinition-lm-identity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T13:54:13+00:00</t>
+    <t>2026-03-17T14:36:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
